--- a/data/directorio.xlsx
+++ b/data/directorio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leonardo.forero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A56BEC9-20D2-42CC-AD24-FCAC78A6A624}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FCF0F4-3D28-4BA2-8EE9-1860648AA8E3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="103">
   <si>
     <t>ID</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>Cra 79 g #54 05 sur</t>
+  </si>
+  <si>
+    <t>Carrera 72B # 5B-90</t>
   </si>
 </sst>
 </file>
@@ -917,6 +920,9 @@
       <c r="F6">
         <v>6013936299</v>
       </c>
+      <c r="G6" t="s">
+        <v>102</v>
+      </c>
       <c r="H6" t="s">
         <v>94</v>
       </c>

--- a/data/directorio.xlsx
+++ b/data/directorio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leonardo.forero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62FCF0F4-3D28-4BA2-8EE9-1860648AA8E3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C67530BB-71C6-40B1-83FB-F1DF488421D7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="9105" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="102">
   <si>
     <t>ID</t>
   </si>
@@ -315,9 +315,6 @@
   </si>
   <si>
     <t>Fundacionmyclaroka@gmail.com</t>
-  </si>
-  <si>
-    <t>Ciudad Bolivar</t>
   </si>
   <si>
     <t xml:space="preserve">Tunjuelito </t>
@@ -807,7 +804,7 @@
         <v>3138830730</v>
       </c>
       <c r="G3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H3" t="s">
         <v>93</v>
@@ -921,7 +918,7 @@
         <v>6013936299</v>
       </c>
       <c r="G6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H6" t="s">
         <v>94</v>
@@ -947,7 +944,7 @@
         <v>69</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
@@ -994,7 +991,7 @@
         <v>74</v>
       </c>
       <c r="H8" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="I8" t="s">
         <v>82</v>
@@ -1032,7 +1029,7 @@
         <v>75</v>
       </c>
       <c r="H9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I9" t="s">
         <v>83</v>
@@ -1067,7 +1064,7 @@
         <v>3214674895</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>94</v>
